--- a/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
@@ -36,12 +36,12 @@
     <t xml:space="preserve">Los Lagos</t>
   </si>
   <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
-    <t xml:space="preserve">San Juan de la Costa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cochamó</t>
   </si>
   <si>
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Río Negro</t>
   </si>
   <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
@@ -72,18 +72,18 @@
     <t xml:space="preserve">Quinchao</t>
   </si>
   <si>
+    <t xml:space="preserve">Chaitén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curaco de Vélez</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaitén</t>
+    <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Muermos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Queilén</t>
   </si>
   <si>
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Hualaihué</t>
   </si>
   <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puerto Varas</t>
   </si>
   <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
     <t xml:space="preserve">Futaleufú</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -562,13 +562,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10307</v>
+        <v>10306</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>154.74</v>
+        <v>165.75</v>
       </c>
     </row>
     <row r="3">
@@ -579,13 +579,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>10306</v>
+        <v>10307</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>152.4</v>
+        <v>165.28</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>131.47</v>
+        <v>144.95</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>130.04</v>
+        <v>139.98</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>129.1</v>
+        <v>139.23</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>127.9</v>
+        <v>137.61</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>125.28</v>
+        <v>134.78</v>
       </c>
     </row>
     <row r="9">
@@ -681,13 +681,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10104</v>
+        <v>10303</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>122.33</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="10">
@@ -698,13 +698,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>10303</v>
+        <v>10104</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>122.09</v>
+        <v>131.98</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>117.53</v>
+        <v>127.37</v>
       </c>
     </row>
     <row r="12">
@@ -738,7 +738,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>115.02</v>
+        <v>126.02</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>113.2</v>
+        <v>123.96</v>
       </c>
     </row>
     <row r="14">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>10204</v>
+        <v>10401</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>110.3</v>
+        <v>119.89</v>
       </c>
     </row>
     <row r="15">
@@ -783,13 +783,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10401</v>
+        <v>10204</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>109.25</v>
+        <v>118.98</v>
       </c>
     </row>
     <row r="16">
@@ -800,13 +800,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10202</v>
+        <v>10106</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>109.01</v>
+        <v>118.33</v>
       </c>
     </row>
     <row r="17">
@@ -817,13 +817,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>10106</v>
+        <v>10202</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>109</v>
+        <v>117.66</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>102.74</v>
+        <v>110.41</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>100.24</v>
+        <v>108.54</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>99.58</v>
+        <v>108.02</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>98.43</v>
+        <v>106.31</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>94.55</v>
+        <v>102.63</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>92.87</v>
+        <v>99.96</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>87.28</v>
+        <v>93.93</v>
       </c>
     </row>
     <row r="25">
@@ -959,7 +959,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>82.4</v>
+        <v>88.96</v>
       </c>
     </row>
     <row r="26">
@@ -976,7 +976,7 @@
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>81.44</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="27">
@@ -987,13 +987,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10109</v>
+        <v>10205</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>77.68</v>
+        <v>83.27</v>
       </c>
     </row>
     <row r="28">
@@ -1004,13 +1004,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10205</v>
+        <v>10109</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>76.88</v>
+        <v>83.03</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>76.8</v>
+        <v>82.33</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>65.73</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>54.44</v>
+        <v>58.22</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:12</t>
+    <t xml:space="preserve">2026-10-05 16:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
